--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A83D9651-E56F-4D40-A027-13DE580BC366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21A3A55-2EDF-409F-8B72-1F89A016F15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="93">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -176,16 +176,159 @@
     <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI</t>
   </si>
   <si>
-    <t>21/10/25</t>
-  </si>
-  <si>
     <t>LIMBO</t>
   </si>
   <si>
     <t>EMILENE CRISTINA DA CUNHA CPF 01709481960</t>
   </si>
   <si>
-    <t>Pedido do seg</t>
+    <t>JUVENAL SIMOES DA COSTA CPF 78208475815</t>
+  </si>
+  <si>
+    <t>21/10/2025</t>
+  </si>
+  <si>
+    <t>CARLOS ROBERTO DA SILVA CPF 72397420678</t>
+  </si>
+  <si>
+    <t>16/10/2025</t>
+  </si>
+  <si>
+    <t>ALYNE RIBEIRO LOPES SHINKAI CPF 5466908746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANADIR TEIXEIRA DA SILVA LIMA                </t>
+  </si>
+  <si>
+    <t>Falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS LAPI VENANCIO                        </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS Justificativa de Dados Divergentes: RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMAGETECH SERVICE LTDA ME                    </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista Justificativa de Dados Divergentes: Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO ROBERTO MAGALHAES CEZAR               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAQUELINE SOARES CORREIA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZENON TELLES BENVINDO MARQUES DA SILVEIRA    </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 20.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA TEIXEIRA INACIO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZPR INDUSTRIA TEXTIL LTDA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FERNANDO MACHADO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO AGENOR ALVES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
+  </si>
+  <si>
+    <t>COPLAN CONTABILIDADE PLANEJAMENTO E ASSESSORI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATIMA USZKO DA SILVA PRONI                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ROBERTO SILVESTRE                     </t>
+  </si>
+  <si>
+    <t>CENTRAL DE ABASTECIMENTO ESCOLAR E LIVRARIA L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO LUIS SALAMI                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CRLV, Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUINALDO DA SILVA JUNIOR                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CRLV, Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RITA DE CASSIA MACHADO FERREIRA              </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) RITA DE CASSIA MACHADO FERREIRA, pois este não consta como con
+dutor na apólice anterior. &lt;br&gt;Neste caso estamos nesta data efet
+uando a recusa desta proposta. Orientamos transmitir um novo proce
+sso como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERONIMO SALUSTIANO DA COSTA JUNIOR          </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026;&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DE FATIMA SAKAMOTO LIMA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMANDO DA SILVA RODRIGUES JUNIOR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOEL FERNANDO VITORIO MORAES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA PRADO COSTA                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANAINA MARCELA RODRIGUES BULHOES            </t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>Limbo</t>
+  </si>
+  <si>
+    <t>HELDER PAULO ZACHARIAS 1718367902</t>
+  </si>
+  <si>
+    <t>Nup cancelamento 21/10/2025</t>
+  </si>
+  <si>
+    <t>18/10/2025</t>
+  </si>
+  <si>
+    <t>JOAO VIRGINIO JUNIOR  8784524430</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO FERREIRA CPF 79496369715</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>Não existe código FIPE para este chassi</t>
   </si>
 </sst>
 </file>
@@ -230,7 +373,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,6 +383,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -531,9 +686,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -588,6 +740,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,7 +1174,7 @@
       <c r="D2" s="24">
         <v>134920718</v>
       </c>
-      <c r="E2" s="47">
+      <c r="E2" s="46">
         <v>3450107023</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -987,10 +1183,10 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="51">
+      <c r="I2" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1007,7 +1203,7 @@
       <c r="D3" s="24">
         <v>134926193</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="47">
         <v>3450107364</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1016,10 +1212,10 @@
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1036,7 +1232,7 @@
       <c r="D4" s="24">
         <v>134927129</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="47">
         <v>3450107397</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1045,39 +1241,39 @@
       <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="50">
         <v>45944</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7">
+    <row r="5" spans="1:9" s="64" customFormat="1">
+      <c r="A5" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="56">
         <v>45944</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="57">
         <v>45950</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="58">
         <v>134924632</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="59">
         <v>3450107287</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="63">
         <v>45944</v>
       </c>
     </row>
@@ -1094,7 +1290,7 @@
       <c r="D6" s="24">
         <v>134943152</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="47">
         <v>3450101006</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1103,10 +1299,10 @@
       <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="50">
         <v>45937</v>
       </c>
     </row>
@@ -1123,7 +1319,7 @@
       <c r="D7" s="24">
         <v>134946354</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="47">
         <v>3450108431</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1132,10 +1328,10 @@
       <c r="G7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="50">
         <v>45945</v>
       </c>
     </row>
@@ -1152,7 +1348,7 @@
       <c r="D8" s="24">
         <v>134948123</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="47">
         <v>3450108519</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1161,10 +1357,10 @@
       <c r="G8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <v>45945</v>
       </c>
     </row>
@@ -1181,7 +1377,7 @@
       <c r="D9" s="24">
         <v>134946767</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="47">
         <v>3450108453</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1190,10 +1386,10 @@
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="50">
         <v>45947</v>
       </c>
     </row>
@@ -1210,7 +1406,7 @@
       <c r="D10" s="24">
         <v>134954190</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="47">
         <v>3450108904</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1219,10 +1415,10 @@
       <c r="G10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="50">
         <v>45945</v>
       </c>
     </row>
@@ -1239,7 +1435,7 @@
       <c r="D11" s="24">
         <v>134948164</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="47">
         <v>3450108520</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1248,10 +1444,10 @@
       <c r="G11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="50">
         <v>45947</v>
       </c>
     </row>
@@ -1268,7 +1464,7 @@
       <c r="D12" s="24">
         <v>134899850</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="47">
         <v>3450105307</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1277,10 +1473,10 @@
       <c r="G12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="50">
         <v>45947</v>
       </c>
     </row>
@@ -1297,7 +1493,7 @@
       <c r="D13" s="24">
         <v>134980185</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <v>3450110510</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1306,10 +1502,10 @@
       <c r="G13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="50">
         <v>45947</v>
       </c>
     </row>
@@ -1326,7 +1522,7 @@
       <c r="D14" s="24">
         <v>134926575</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>3450107386</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1335,10 +1531,10 @@
       <c r="G14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1355,7 +1551,7 @@
       <c r="D15" s="24">
         <v>134912411</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="47">
         <v>3450106517</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1364,10 +1560,10 @@
       <c r="G15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="50">
         <v>45943</v>
       </c>
     </row>
@@ -1384,7 +1580,7 @@
       <c r="D16" s="24">
         <v>134933365</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="47">
         <v>3450107793</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1393,10 +1589,10 @@
       <c r="G16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1413,7 +1609,7 @@
       <c r="D17" s="24">
         <v>134923813</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <v>3450107166</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1422,10 +1618,10 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1442,7 +1638,7 @@
       <c r="D18" s="24">
         <v>134873058</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="47">
         <v>3450100324</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1451,10 +1647,10 @@
       <c r="G18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -1471,7 +1667,7 @@
       <c r="D19" s="24">
         <v>134934767</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="47">
         <v>3450107870</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1480,10 +1676,10 @@
       <c r="G19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="50">
         <v>45944</v>
       </c>
     </row>
@@ -1491,8 +1687,8 @@
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="49"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="48"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="9"/>
@@ -1504,7 +1700,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="24"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="50"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
       <c r="I21" s="26"/>
@@ -1949,351 +2145,775 @@
       <c r="B2" s="7">
         <v>45940</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D2" s="24" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="18">
         <v>3450103800</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="26"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="B3" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C3" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450101534</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450102931</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="50"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="67">
+        <v>3450101985</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="50"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C6" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D6" s="69">
+        <v>134893205</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450105054</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="50">
+        <v>45940</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C7" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D7" s="69">
+        <v>134898334</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450105219</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C8" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D8" s="69">
+        <v>134908821</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450106165</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C9" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D9" s="69">
+        <v>134913987</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450106682</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C10" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D10" s="69">
+        <v>134902221</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450105582</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45950</v>
+      </c>
+      <c r="C11" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D11" s="69">
+        <v>134954244</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450108915</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="50">
+        <v>45950</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C12" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D12" s="69">
+        <v>134962076</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450109190</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="50">
+        <v>45946</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C13" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D13" s="69">
+        <v>134898688</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450105230</v>
+      </c>
+      <c r="F13" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D14" s="69">
+        <v>134981455</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450110609</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="50">
+        <v>45950</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C15" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D15" s="69">
+        <v>134885981</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450104504</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="50">
+        <v>45947</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C16" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D16" s="69">
+        <v>134987089</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450111115</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="50">
+        <v>45947</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="B17" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C17" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D17" s="69">
+        <v>134998920</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450112402</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="50">
+        <v>45950</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C18" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D18" s="69">
+        <v>134886837</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450104560</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="50">
+        <v>45940</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45950</v>
+      </c>
+      <c r="C19" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D19" s="69">
+        <v>135013874</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450113348</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="50">
+        <v>45950</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C20" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D20" s="69">
+        <v>134903935</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450105769</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C21" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D21" s="69">
+        <v>134966734</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450109707</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="50">
+        <v>45946</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C22" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D22" s="69">
+        <v>134838338</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450101578</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="50">
+        <v>45944</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C23" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D23" s="69">
+        <v>134831981</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450101325</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" s="50">
+        <v>45944</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C24" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D24" s="69">
+        <v>135033178</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450114844</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="50">
+        <v>45951</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C25" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D25" s="69">
+        <v>134884688</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450104405</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="50">
+        <v>45940</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C26" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D26" s="69">
+        <v>134886908</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450104581</v>
+      </c>
+      <c r="F26" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="50">
+        <v>45940</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C27" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D27" s="69">
+        <v>134909904</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450101864</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="50">
+        <v>45938</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C28" s="27">
+        <v>45951</v>
+      </c>
+      <c r="D28" s="69">
+        <v>134911954</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450106506</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="50">
+        <v>45943</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="26"/>
     </row>
     <row r="30" spans="1:9">
@@ -2584,7 +3204,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2611,7 +3231,7 @@
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" customWidth="1"/>
     <col min="9" max="9" width="21" style="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2640,7 +3260,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2648,37 +3268,79 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="27">
+        <v>45952</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="72">
+        <v>3450112590</v>
+      </c>
+      <c r="F2" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="27">
+        <v>45952</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="72">
+        <v>3450112666</v>
+      </c>
+      <c r="F3" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45952</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="72">
+        <v>3450112193</v>
+      </c>
+      <c r="F4" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3804,7 +4466,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -3820,8 +4482,8 @@
       <c r="D2" s="24"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="37"/>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9">
@@ -3833,8 +4495,8 @@
       <c r="D3" s="24"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="37"/>
       <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9">
@@ -3846,8 +4508,8 @@
       <c r="D4" s="24"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9">
@@ -3859,8 +4521,8 @@
       <c r="D5" s="24"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9">
@@ -3872,8 +4534,8 @@
       <c r="D6" s="24"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9">
@@ -3885,8 +4547,8 @@
       <c r="D7" s="24"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9">
@@ -3898,8 +4560,8 @@
       <c r="D8" s="24"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9">
@@ -3911,8 +4573,8 @@
       <c r="D9" s="24"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:9">
@@ -3924,8 +4586,8 @@
       <c r="D10" s="24"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9">
@@ -3937,8 +4599,8 @@
       <c r="D11" s="24"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9">
@@ -3950,8 +4612,8 @@
       <c r="D12" s="24"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9">
@@ -3963,8 +4625,8 @@
       <c r="D13" s="24"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:9">
@@ -3976,8 +4638,8 @@
       <c r="D14" s="24"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:9">
@@ -3989,8 +4651,8 @@
       <c r="D15" s="24"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:9">
@@ -4002,8 +4664,8 @@
       <c r="D16" s="24"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -4015,8 +4677,8 @@
       <c r="D17" s="24"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="26"/>
     </row>
     <row r="18" spans="1:9">
@@ -4028,8 +4690,8 @@
       <c r="D18" s="24"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:9">
@@ -4037,9 +4699,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="9"/>
       <c r="I19" s="26"/>
     </row>
@@ -4050,7 +4712,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="9"/>
       <c r="I20" s="26"/>
     </row>
@@ -4061,7 +4723,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="9"/>
       <c r="I21" s="26"/>
     </row>
@@ -4072,7 +4734,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="9"/>
       <c r="I22" s="26"/>
     </row>
@@ -4083,7 +4745,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="9"/>
       <c r="I23" s="26"/>
     </row>
@@ -4094,7 +4756,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="9"/>
       <c r="I24" s="26"/>
     </row>
@@ -4525,7 +5187,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4558,8 +5220,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="22"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="26"/>
@@ -5716,51 +6378,67 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="0b21122b788e66690c7828fa6fbd4a35">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8036ee6e27b0b3bdae29363f3ddd68e9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -5809,12 +6487,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -5823,12 +6501,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -5911,7 +6589,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -5930,7 +6608,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -5963,7 +6641,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6046,8 +6724,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6136,77 +6814,61 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBAD38D8-40DC-4D8D-99B3-A9CEA7784112}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3E70DC1-B749-459D-B5AE-A731D16F8E87}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21A3A55-2EDF-409F-8B72-1F89A016F15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B35946A9-2A12-4B96-AA42-977E6E6BC03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="145">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -329,6 +329,172 @@
   </si>
   <si>
     <t>Não existe código FIPE para este chassi</t>
+  </si>
+  <si>
+    <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>FLAVIO ARAUJO DE MENDONCA CPF 74008412700</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>CHARLIES PITER SANTOS LIMA CPF 09998356709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JURACI FERREIRA DE ALMEIDA CPF 54584620687 </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Apl 134987762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE GONCALVES DE SOUZA                     </t>
+  </si>
+  <si>
+    <t>Para 
+a avaliação e liberação da emissão da proposta em referência, agra
+decemos retornar o formulário anexo preenchido. Declaração de origem de recursos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDEMIR BENTO CAPATO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOEL MARQUES                                 </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGNO DE LIMA FERREIRA ME                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBEN GABRIEL MENDOSA MENDIETA               </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO Foto: Chassi - SEG. TIROU FOTO DO LOCAL INCORRETO, E NÃO CORRIGIU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS DONIZETE DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOEL IVO CABRAL                              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE Ñ CORRIGIU AS FOTOS INCORRETAS - PRAZO EXP FOTOS INCORRETAS: CRLV, Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro, Motor e placa, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARCY BITTENCOURT                            </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO Fotos: Frente e lateral ESQUERD/DIR, Traseira e lateral ESQ/DIR, Motor, Painel, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONEL FERREIRA DE FRANCA                    </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAUL BARROZO DA MOTTA JUNIOR                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado. KM PARCIAL.</t>
+  </si>
+  <si>
+    <t>FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTER BATISTA FREIRE                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi. Justificativa de Dados Divergentes: SEM DIVERGÊNCIA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARLA GARCIA GONCALVES                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIZABETH NAZARIO CARVALHO                   </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro Justificativa de Dados Divergentes: a e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO VINICIUS DE ARAUJO CASTRO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nº do 
+chassi difere do docto do veículo, por gentileza transmitir um nov
+o processo com o veículo correto.&lt;br&gt;&lt;br&gt;Chassi transmitido: 9C6SG
+6210M0002763&lt;br&gt;Chassi correto conforme CRLV: 9C6SG6210N0012203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO MEDEIROS FERNANDES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE PEREIRA ROGERIO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CRLV. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODOLFO VIEIRA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAVIO DOS SANTOS GONCALVES                  </t>
+  </si>
+  <si>
+    <t>Proposta em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANE ALCANTARA                            </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve trata-se de renovação congênere, sendo renovada
+com 231 dias em atraso e não houve sinistro , conforme regra exclu
+i-se seis classes de bônus, assim sendo o correto bônus 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA MARANGONI CUSTODIO SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA DA SILVA NASCIMENTO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORDAO REPRESENTACAO E COMERCIO DE ALIMENTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO DA SILVA BARROS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAILDA BARRETO                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANA GONCALVES OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANE MARTINIANO PESTANA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LUCIA DANTAS MORGADO ANDRADE           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL MARIANO CHAGAS DA SILVA              </t>
   </si>
 </sst>
 </file>
@@ -610,7 +776,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -660,7 +826,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -764,7 +929,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -774,16 +938,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,13 +1349,13 @@
       <c r="B2" s="7">
         <v>45944</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45950</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <v>134920718</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="45">
         <v>3450107023</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -1183,10 +1364,10 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="50">
+      <c r="I2" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1197,13 +1378,13 @@
       <c r="B3" s="7">
         <v>45944</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45950</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>134926193</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E3" s="46">
         <v>3450107364</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1212,10 +1393,10 @@
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="50">
+      <c r="I3" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1226,13 +1407,13 @@
       <c r="B4" s="7">
         <v>45944</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45950</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>134927129</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="46">
         <v>3450107397</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1241,39 +1422,39 @@
       <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="49">
         <v>45944</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="64" customFormat="1">
-      <c r="A5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="56">
+    <row r="5" spans="1:9" s="63" customFormat="1">
+      <c r="A5" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="55">
         <v>45944</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="56">
         <v>45950</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="57">
         <v>134924632</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="58">
         <v>3450107287</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="62" t="s">
+      <c r="H5" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="62">
         <v>45944</v>
       </c>
     </row>
@@ -1284,13 +1465,13 @@
       <c r="B6" s="7">
         <v>45937</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45950</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>134943152</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="46">
         <v>3450101006</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1299,10 +1480,10 @@
       <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="49">
         <v>45937</v>
       </c>
     </row>
@@ -1313,25 +1494,25 @@
       <c r="B7" s="7">
         <v>45945</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45950</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>134946354</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="46">
         <v>3450108431</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="49">
         <v>45945</v>
       </c>
     </row>
@@ -1342,25 +1523,25 @@
       <c r="B8" s="7">
         <v>45945</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45950</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>134948123</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="46">
         <v>3450108519</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="49">
         <v>45945</v>
       </c>
     </row>
@@ -1371,13 +1552,13 @@
       <c r="B9" s="7">
         <v>45940</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45950</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>134946767</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="46">
         <v>3450108453</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1386,10 +1567,10 @@
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -1400,13 +1581,13 @@
       <c r="B10" s="7">
         <v>45945</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45950</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>134954190</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="46">
         <v>3450108904</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1415,10 +1596,10 @@
       <c r="G10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="49">
         <v>45945</v>
       </c>
     </row>
@@ -1429,13 +1610,13 @@
       <c r="B11" s="7">
         <v>45945</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45950</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>134948164</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="46">
         <v>3450108520</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1444,10 +1625,10 @@
       <c r="G11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -1458,13 +1639,13 @@
       <c r="B12" s="7">
         <v>45943</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45950</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>134899850</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="46">
         <v>3450105307</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1473,10 +1654,10 @@
       <c r="G12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -1487,13 +1668,13 @@
       <c r="B13" s="7">
         <v>45947</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45950</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>134980185</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="46">
         <v>3450110510</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1502,10 +1683,10 @@
       <c r="G13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -1516,13 +1697,13 @@
       <c r="B14" s="7">
         <v>45944</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45950</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>134926575</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="46">
         <v>3450107386</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1531,10 +1712,10 @@
       <c r="G14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1545,13 +1726,13 @@
       <c r="B15" s="7">
         <v>45943</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45950</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>134912411</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="46">
         <v>3450106517</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1560,10 +1741,10 @@
       <c r="G15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="51" t="s">
+      <c r="H15" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -1574,13 +1755,13 @@
       <c r="B16" s="7">
         <v>45944</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45950</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>134933365</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="46">
         <v>3450107793</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1589,10 +1770,10 @@
       <c r="G16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="51" t="s">
+      <c r="H16" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1603,13 +1784,13 @@
       <c r="B17" s="7">
         <v>45944</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45950</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>134923813</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="46">
         <v>3450107166</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1618,10 +1799,10 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1632,13 +1813,13 @@
       <c r="B18" s="7">
         <v>45936</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45950</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>134873058</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="46">
         <v>3450100324</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1647,10 +1828,10 @@
       <c r="G18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="50">
+      <c r="I18" s="49">
         <v>45936</v>
       </c>
     </row>
@@ -1661,13 +1842,13 @@
       <c r="B19" s="7">
         <v>45944</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45950</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>134934767</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="46">
         <v>3450107870</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1676,10 +1857,10 @@
       <c r="G19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="51" t="s">
+      <c r="H19" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="50">
+      <c r="I19" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -1687,250 +1868,250 @@
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="48"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="47"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="24"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="49"/>
+      <c r="F21" s="48"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="24"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="18"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="24"/>
+      <c r="D23" s="23"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="24"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="18"/>
       <c r="F24" s="19"/>
       <c r="G24" s="20"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="24"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="18"/>
       <c r="F25" s="19"/>
       <c r="G25" s="20"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="24"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="18"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="26"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="24"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="18"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="24"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="18"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="24"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="18"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="24"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="18"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="24"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="18"/>
       <c r="F31" s="19"/>
       <c r="G31" s="20"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="24"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="19"/>
       <c r="G32" s="20"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="24"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="20"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="24"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="18"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="24"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="18"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="24"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="24"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="18"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="26"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="18"/>
       <c r="F38" s="12"/>
-      <c r="G38" s="23"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="26"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="24"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="18"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="23"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="26"/>
+      <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="24"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="18"/>
       <c r="F40" s="19"/>
       <c r="G40" s="20"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="26"/>
+      <c r="I40" s="25"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="24"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="18"/>
       <c r="F41" s="19"/>
       <c r="G41" s="20"/>
       <c r="H41" s="9"/>
-      <c r="I41" s="26"/>
+      <c r="I41" s="25"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="15"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
@@ -2145,10 +2326,10 @@
       <c r="B2" s="7">
         <v>45940</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45951</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="18">
@@ -2157,11 +2338,11 @@
       <c r="F2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="12"/>
-      <c r="I2" s="50"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -2170,10 +2351,10 @@
       <c r="B3" s="7">
         <v>45940</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45951</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="18">
@@ -2182,23 +2363,23 @@
       <c r="F3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="I3" s="50"/>
+      <c r="I3" s="49"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45951</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="18">
@@ -2207,11 +2388,11 @@
       <c r="F4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="13"/>
-      <c r="I4" s="50"/>
+      <c r="I4" s="49"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -2220,23 +2401,23 @@
       <c r="B5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45951</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="65">
         <v>3450101985</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="13"/>
-      <c r="I5" s="50"/>
+      <c r="I5" s="49"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -2245,25 +2426,25 @@
       <c r="B6" s="7">
         <v>45940</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45951</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="23">
         <v>134893205</v>
       </c>
       <c r="E6" s="18">
         <v>3450105054</v>
       </c>
-      <c r="F6" s="65" t="s">
+      <c r="F6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="49">
         <v>45940</v>
       </c>
     </row>
@@ -2274,25 +2455,25 @@
       <c r="B7" s="7">
         <v>45943</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45951</v>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="23">
         <v>134898334</v>
       </c>
       <c r="E7" s="18">
         <v>3450105219</v>
       </c>
-      <c r="F7" s="65" t="s">
+      <c r="F7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2303,25 +2484,25 @@
       <c r="B8" s="7">
         <v>45943</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45951</v>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="23">
         <v>134908821</v>
       </c>
       <c r="E8" s="18">
         <v>3450106165</v>
       </c>
-      <c r="F8" s="65" t="s">
+      <c r="F8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2332,25 +2513,25 @@
       <c r="B9" s="7">
         <v>45943</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45951</v>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="23">
         <v>134913987</v>
       </c>
       <c r="E9" s="18">
         <v>3450106682</v>
       </c>
-      <c r="F9" s="65" t="s">
+      <c r="F9" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2361,25 +2542,25 @@
       <c r="B10" s="7">
         <v>45943</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45951</v>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="23">
         <v>134902221</v>
       </c>
       <c r="E10" s="18">
         <v>3450105582</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2390,25 +2571,25 @@
       <c r="B11" s="7">
         <v>45950</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45951</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="23">
         <v>134954244</v>
       </c>
       <c r="E11" s="18">
         <v>3450108915</v>
       </c>
-      <c r="F11" s="65" t="s">
+      <c r="F11" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="49">
         <v>45950</v>
       </c>
     </row>
@@ -2419,25 +2600,25 @@
       <c r="B12" s="7">
         <v>45946</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45951</v>
       </c>
-      <c r="D12" s="69">
+      <c r="D12" s="23">
         <v>134962076</v>
       </c>
       <c r="E12" s="18">
         <v>3450109190</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="24" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="49">
         <v>45946</v>
       </c>
     </row>
@@ -2448,25 +2629,25 @@
       <c r="B13" s="7">
         <v>45943</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45951</v>
       </c>
-      <c r="D13" s="69">
+      <c r="D13" s="23">
         <v>134898688</v>
       </c>
       <c r="E13" s="18">
         <v>3450105230</v>
       </c>
-      <c r="F13" s="65" t="s">
+      <c r="F13" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2477,25 +2658,25 @@
       <c r="B14" s="7">
         <v>45951</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45951</v>
       </c>
-      <c r="D14" s="69">
+      <c r="D14" s="23">
         <v>134981455</v>
       </c>
       <c r="E14" s="18">
         <v>3450110609</v>
       </c>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="49">
         <v>45950</v>
       </c>
     </row>
@@ -2506,25 +2687,25 @@
       <c r="B15" s="7">
         <v>45940</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45951</v>
       </c>
-      <c r="D15" s="69">
+      <c r="D15" s="23">
         <v>134885981</v>
       </c>
       <c r="E15" s="18">
         <v>3450104504</v>
       </c>
-      <c r="F15" s="65" t="s">
+      <c r="F15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -2535,25 +2716,25 @@
       <c r="B16" s="7">
         <v>45947</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45951</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="23">
         <v>134987089</v>
       </c>
       <c r="E16" s="18">
         <v>3450111115</v>
       </c>
-      <c r="F16" s="65" t="s">
+      <c r="F16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="24" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="49">
         <v>45947</v>
       </c>
     </row>
@@ -2564,25 +2745,25 @@
       <c r="B17" s="7">
         <v>45946</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45951</v>
       </c>
-      <c r="D17" s="69">
+      <c r="D17" s="23">
         <v>134998920</v>
       </c>
       <c r="E17" s="18">
         <v>3450112402</v>
       </c>
-      <c r="F17" s="65" t="s">
+      <c r="F17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="49">
         <v>45950</v>
       </c>
     </row>
@@ -2593,25 +2774,25 @@
       <c r="B18" s="7">
         <v>45940</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45951</v>
       </c>
-      <c r="D18" s="69">
+      <c r="D18" s="23">
         <v>134886837</v>
       </c>
       <c r="E18" s="18">
         <v>3450104560</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="50">
+      <c r="I18" s="49">
         <v>45940</v>
       </c>
     </row>
@@ -2622,25 +2803,25 @@
       <c r="B19" s="7">
         <v>45950</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45951</v>
       </c>
-      <c r="D19" s="69">
+      <c r="D19" s="23">
         <v>135013874</v>
       </c>
       <c r="E19" s="18">
         <v>3450113348</v>
       </c>
-      <c r="F19" s="65" t="s">
+      <c r="F19" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="24" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="50">
+      <c r="I19" s="49">
         <v>45950</v>
       </c>
     </row>
@@ -2651,25 +2832,25 @@
       <c r="B20" s="7">
         <v>45943</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45951</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="23">
         <v>134903935</v>
       </c>
       <c r="E20" s="18">
         <v>3450105769</v>
       </c>
-      <c r="F20" s="65" t="s">
+      <c r="F20" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="24" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="50">
+      <c r="I20" s="49">
         <v>45943</v>
       </c>
     </row>
@@ -2680,25 +2861,25 @@
       <c r="B21" s="7">
         <v>45946</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>45951</v>
       </c>
-      <c r="D21" s="69">
+      <c r="D21" s="23">
         <v>134966734</v>
       </c>
       <c r="E21" s="18">
         <v>3450109707</v>
       </c>
-      <c r="F21" s="65" t="s">
+      <c r="F21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="24" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I21" s="50">
+      <c r="I21" s="49">
         <v>45946</v>
       </c>
     </row>
@@ -2709,25 +2890,25 @@
       <c r="B22" s="7">
         <v>45946</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>45951</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="23">
         <v>134838338</v>
       </c>
       <c r="E22" s="18">
         <v>3450101578</v>
       </c>
-      <c r="F22" s="65" t="s">
+      <c r="F22" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="71" t="s">
+      <c r="H22" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="50">
+      <c r="I22" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -2738,25 +2919,25 @@
       <c r="B23" s="7">
         <v>45938</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>45951</v>
       </c>
-      <c r="D23" s="69">
+      <c r="D23" s="23">
         <v>134831981</v>
       </c>
       <c r="E23" s="18">
         <v>3450101325</v>
       </c>
-      <c r="F23" s="65" t="s">
+      <c r="F23" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="H23" s="71" t="s">
+      <c r="H23" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="50">
+      <c r="I23" s="49">
         <v>45944</v>
       </c>
     </row>
@@ -2767,25 +2948,25 @@
       <c r="B24" s="7">
         <v>45954</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>45951</v>
       </c>
-      <c r="D24" s="69">
+      <c r="D24" s="23">
         <v>135033178</v>
       </c>
       <c r="E24" s="18">
         <v>3450114844</v>
       </c>
-      <c r="F24" s="65" t="s">
+      <c r="F24" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I24" s="50">
+      <c r="I24" s="49">
         <v>45951</v>
       </c>
     </row>
@@ -2796,25 +2977,25 @@
       <c r="B25" s="7">
         <v>45940</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>45951</v>
       </c>
-      <c r="D25" s="69">
+      <c r="D25" s="23">
         <v>134884688</v>
       </c>
       <c r="E25" s="18">
         <v>3450104405</v>
       </c>
-      <c r="F25" s="65" t="s">
+      <c r="F25" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="50">
+      <c r="I25" s="49">
         <v>45940</v>
       </c>
     </row>
@@ -2825,25 +3006,25 @@
       <c r="B26" s="7">
         <v>45940</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>45951</v>
       </c>
-      <c r="D26" s="69">
+      <c r="D26" s="23">
         <v>134886908</v>
       </c>
       <c r="E26" s="18">
         <v>3450104581</v>
       </c>
-      <c r="F26" s="65" t="s">
+      <c r="F26" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="70" t="s">
+      <c r="H26" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="50">
+      <c r="I26" s="49">
         <v>45940</v>
       </c>
     </row>
@@ -2854,25 +3035,25 @@
       <c r="B27" s="7">
         <v>45938</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>45951</v>
       </c>
-      <c r="D27" s="69">
+      <c r="D27" s="23">
         <v>134909904</v>
       </c>
       <c r="E27" s="18">
         <v>3450101864</v>
       </c>
-      <c r="F27" s="65" t="s">
+      <c r="F27" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I27" s="50">
+      <c r="I27" s="49">
         <v>45938</v>
       </c>
     </row>
@@ -2883,93 +3064,93 @@
       <c r="B28" s="7">
         <v>45943</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>45951</v>
       </c>
-      <c r="D28" s="69">
+      <c r="D28" s="23">
         <v>134911954</v>
       </c>
       <c r="E28" s="18">
         <v>3450106506</v>
       </c>
-      <c r="F28" s="65" t="s">
+      <c r="F28" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="50">
+      <c r="I28" s="49">
         <v>45943</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="34"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="20"/>
       <c r="H29" s="15"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
       <c r="G30" s="20"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="18"/>
       <c r="F31" s="12"/>
       <c r="G31" s="20"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="12"/>
       <c r="G32" s="20"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="18"/>
       <c r="F33" s="12"/>
       <c r="G33" s="20"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="15"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -2980,7 +3161,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -2991,7 +3172,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -3222,7 +3403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
@@ -3232,7 +3413,7 @@
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.140625" customWidth="1"/>
-    <col min="9" max="9" width="21" style="26" customWidth="1"/>
+    <col min="9" max="9" width="21" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3260,7 +3441,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3271,24 +3452,25 @@
       <c r="B2" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45952</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="68">
         <v>3450112590</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="68" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="51" t="s">
         <v>87</v>
       </c>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -3297,24 +3479,25 @@
       <c r="B3" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45952</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="72">
+      <c r="E3" s="69">
         <v>3450112666</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="68" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="51" t="s">
         <v>87</v>
       </c>
+      <c r="I3" s="49"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3323,380 +3506,959 @@
       <c r="B4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45952</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="69">
         <v>3450112193</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="68" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="51" t="s">
         <v>92</v>
       </c>
+      <c r="I4" s="49"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="69">
+        <v>3450111533</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="49"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="69">
+        <v>3450114162</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="49"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="75">
+        <v>45936</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="69">
+        <v>3450100160</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="49"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="75">
+        <v>45938</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D8" s="74">
+        <v>134849892</v>
+      </c>
+      <c r="E8" s="71">
+        <v>3450102436</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="49">
+        <v>45940</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="75">
+        <v>45944</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D9" s="74">
+        <v>134903636</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450105703</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="49">
+        <v>45951</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="75">
+        <v>45943</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D10" s="74">
+        <v>134913758</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450106650</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="75">
+        <v>45940</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D11" s="74">
+        <v>134928422</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450104702</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="49">
+        <v>45940</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="75">
+        <v>45946</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D12" s="74">
+        <v>134965026</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450109465</v>
+      </c>
+      <c r="F12" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" s="49">
+        <v>45946</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="75">
+        <v>45946</v>
+      </c>
+      <c r="C13" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D13" s="74">
+        <v>134972980</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450110170</v>
+      </c>
+      <c r="F13" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="49">
+        <v>45946</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C14" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D14" s="74">
+        <v>134986262</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450110972</v>
+      </c>
+      <c r="F14" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="49">
+        <v>45947</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C15" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D15" s="74">
+        <v>134987136</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450111137</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="49">
+        <v>45947</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="B16" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C16" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D16" s="74">
+        <v>134986230</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450110950</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C17" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D17" s="74">
+        <v>134988232</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450111324</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C18" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D18" s="74">
+        <v>134988419</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450111368</v>
+      </c>
+      <c r="F18" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D19" s="74">
+        <v>134993720</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450111841</v>
+      </c>
+      <c r="F19" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="75">
+        <v>45947</v>
+      </c>
+      <c r="C20" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D20" s="74">
+        <v>134996719</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450112160</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C21" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D21" s="74">
+        <v>134998645</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450112370</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C22" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D22" s="74">
+        <v>134986172</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450110940</v>
+      </c>
+      <c r="F22" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="76" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="49">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C23" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D23" s="74">
+        <v>134990611</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450111599</v>
+      </c>
+      <c r="F23" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C24" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D24" s="74">
+        <v>134988396</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450111357</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="49">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45951</v>
+      </c>
+      <c r="C25" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D25" s="74">
+        <v>135029467</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450114580</v>
+      </c>
+      <c r="F25" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="49">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C26" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D26" s="74">
+        <v>134861748</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450103118</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="49">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C27" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D27" s="74">
+        <v>134858457</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450102744</v>
+      </c>
+      <c r="F27" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="I27" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C28" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D28" s="74">
+        <v>134948867</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450107419</v>
+      </c>
+      <c r="F28" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C29" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D29" s="74">
+        <v>135049650</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450116428</v>
+      </c>
+      <c r="F29" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="49">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C30" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D30" s="74">
+        <v>134916937</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450106781</v>
+      </c>
+      <c r="F30" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C31" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D31" s="74">
+        <v>134917784</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450106870</v>
+      </c>
+      <c r="F31" s="70" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C32" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D32" s="74">
+        <v>134923879</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450107177</v>
+      </c>
+      <c r="F32" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C33" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D33" s="74">
+        <v>134924247</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450107232</v>
+      </c>
+      <c r="F33" s="70" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C34" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D34" s="74">
+        <v>134928778</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450104669</v>
+      </c>
+      <c r="F34" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="49">
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C35" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D35" s="74">
+        <v>134932121</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3450107716</v>
+      </c>
+      <c r="F35" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C36" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D36" s="74">
+        <v>134934017</v>
+      </c>
+      <c r="E36" s="18">
+        <v>3450107859</v>
+      </c>
+      <c r="F36" s="70" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="49">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="15"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
@@ -3706,7 +4468,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
@@ -3716,7 +4478,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
@@ -3726,7 +4488,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="8"/>
       <c r="C41" s="7"/>
@@ -3736,43 +4498,20 @@
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A36" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B20" xr:uid="{3A74ADBB-8B31-4909-8F59-DD30BCD653AA}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B20" xr:uid="{3A74ADBB-8B31-4909-8F59-DD30BCD653AA}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3829,12 +4568,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="28"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="8"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="29"/>
+      <c r="G2" s="28"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -3842,12 +4581,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="28"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="8"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="29"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3855,12 +4594,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="28"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="29"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3868,12 +4607,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="8"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="29"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3881,12 +4620,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="8"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="29"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3894,12 +4633,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="28"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="8"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="29"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -3907,12 +4646,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="28"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="8"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="29"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="26"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -3920,12 +4659,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="28"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="8"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="26"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -3933,12 +4672,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="28"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="8"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -3946,12 +4685,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="29"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -3959,12 +4698,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="28"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="8"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="29"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -3972,12 +4711,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="28"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="8"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -3985,12 +4724,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="29"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -3998,23 +4737,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="28"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="8"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="29"/>
+      <c r="G15" s="28"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="28"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="8"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="29"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4025,7 +4764,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4036,7 +4775,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4047,7 +4786,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4058,7 +4797,7 @@
       <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4466,7 +5205,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4478,232 +5217,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="26"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="26"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="26"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="26"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="26"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="26"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="26"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="26"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="26"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="26"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="26"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="26"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="32"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4712,9 +5451,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="32"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4723,9 +5462,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="32"/>
+      <c r="G21" s="31"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -4734,9 +5473,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="32"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -4745,9 +5484,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="32"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -4756,9 +5495,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -4769,7 +5508,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -4780,7 +5519,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="26"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -4791,7 +5530,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -4802,7 +5541,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -4813,7 +5552,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -4824,7 +5563,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -4835,7 +5574,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -4846,7 +5585,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -4857,7 +5596,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -4868,7 +5607,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -4879,7 +5618,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -5168,63 +5907,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="12"/>
       <c r="G2" s="20"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="36"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="12"/>
       <c r="G4" s="20"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12"/>
       <c r="G5" s="20"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -6387,53 +7126,46 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6815,46 +7547,53 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6862,13 +7601,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3E70DC1-B749-459D-B5AE-A731D16F8E87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6A422DA-5A64-429E-A048-04B376314D8C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B35946A9-2A12-4B96-AA42-977E6E6BC03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC4D956E-1B0A-4881-ABE3-1B71E206A5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="175">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -319,7 +319,7 @@
     <t>18/10/2025</t>
   </si>
   <si>
-    <t>JOAO VIRGINIO JUNIOR  8784524430</t>
+    <t>JOAO VIRGINIO JUNIOR  08784524430</t>
   </si>
   <si>
     <t>CARLOS ALBERTO FERREIRA CPF 79496369715</t>
@@ -495,6 +495,102 @@
   </si>
   <si>
     <t xml:space="preserve">GABRIEL MARIANO CHAGAS DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO COSTA VEIGA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA RIBEIRO MOTA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNEIA RANGEL DA SILVA DOS SANTOS            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ALBERTO DE OLIVEIRA BERTINO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QATAR PHARMA LTDA ME                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BONUS SOLAR COMERCIO E IMPORTACAO LTDA EPP   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRO MARCELO QUADROS CABRAL                </t>
+  </si>
+  <si>
+    <t>Veiculo informado é divergente do calculado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANELUZA APARECIDA CLARO FAUSTO              </t>
+  </si>
+  <si>
+    <t>Divergência de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRACIELLE MAYRA RODRIGUES                    </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINDOCY DE JESUS MOREIRA COSTA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA MENEZES VIEIRA                       </t>
+  </si>
+  <si>
+    <t>Divergência de bônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVONETE ANTONIA GRESPAN                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) IVONETE ANTONIA GRESPAN, pois este não consta como condutor na
+apólice anterior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NILSON PEREIRA LEITAO                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) NILSON PEREIRA LEITAO , pois este não consta como condutor na
+apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SACOLAO JL LTDA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO FAITAO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO HENRIQUE DOS SANTOS SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREDSON RODRIGUES COUTINHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS TRANSPORTES PROMISSAO LTDA ME             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP COMERCIO DE PESCADOS E FRUTOS DO MAR LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCE MARIA KAIM DALLA VECHIA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEOMIR VALERIO DA SILVA                      </t>
+  </si>
+  <si>
+    <t>PADARIA E CONFEITARIA LISBOA CARAGUATATUBA ME</t>
+  </si>
+  <si>
+    <t>D BRUNO DE LIMA COMERCIO DE BEBIDAS E GELO ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 468 393 ALESSANDRO MIRANDA COIMBRA ME     </t>
   </si>
 </sst>
 </file>
@@ -776,7 +872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -947,24 +1043,29 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3461,7 +3562,7 @@
       <c r="E2" s="68">
         <v>3450112590</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="73" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -3488,7 +3589,7 @@
       <c r="E3" s="69">
         <v>3450112666</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="73" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -3515,7 +3616,7 @@
       <c r="E4" s="69">
         <v>3450112193</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="73" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -3542,7 +3643,7 @@
       <c r="E5" s="69">
         <v>3450111533</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="73" t="s">
         <v>94</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -3569,7 +3670,7 @@
       <c r="E6" s="69">
         <v>3450114162</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="73" t="s">
         <v>96</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -3584,19 +3685,19 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="72">
         <v>45936</v>
       </c>
       <c r="C7" s="26">
         <v>45952</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="71" t="s">
         <v>85</v>
       </c>
       <c r="E7" s="69">
         <v>3450100160</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="74" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20" t="s">
@@ -3611,25 +3712,25 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="72">
         <v>45938</v>
       </c>
       <c r="C8" s="26">
         <v>45952</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="23">
         <v>134849892</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="70">
         <v>3450102436</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="75" t="s">
         <v>101</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="77" t="s">
+      <c r="H8" s="51" t="s">
         <v>102</v>
       </c>
       <c r="I8" s="49">
@@ -3640,19 +3741,19 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="75">
+      <c r="B9" s="72">
         <v>45944</v>
       </c>
       <c r="C9" s="26">
         <v>45952</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="23">
         <v>134903636</v>
       </c>
       <c r="E9" s="18">
         <v>3450105703</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="12" t="s">
         <v>103</v>
       </c>
       <c r="G9" s="20" t="s">
@@ -3669,25 +3770,25 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="75">
+      <c r="B10" s="72">
         <v>45943</v>
       </c>
       <c r="C10" s="26">
         <v>45952</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="23">
         <v>134913758</v>
       </c>
       <c r="E10" s="18">
         <v>3450106650</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="12" t="s">
         <v>104</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="76" t="s">
+      <c r="H10" s="50" t="s">
         <v>105</v>
       </c>
       <c r="I10" s="49">
@@ -3698,19 +3799,19 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="72">
         <v>45940</v>
       </c>
       <c r="C11" s="26">
         <v>45952</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="23">
         <v>134928422</v>
       </c>
       <c r="E11" s="18">
         <v>3450104702</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="12" t="s">
         <v>106</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -3727,19 +3828,19 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="72">
         <v>45946</v>
       </c>
       <c r="C12" s="26">
         <v>45952</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="23">
         <v>134965026</v>
       </c>
       <c r="E12" s="18">
         <v>3450109465</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="12" t="s">
         <v>108</v>
       </c>
       <c r="G12" s="22" t="s">
@@ -3756,19 +3857,19 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="72">
         <v>45946</v>
       </c>
       <c r="C13" s="26">
         <v>45952</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="23">
         <v>134972980</v>
       </c>
       <c r="E13" s="18">
         <v>3450110170</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="12" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -3785,19 +3886,19 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="72">
         <v>45947</v>
       </c>
       <c r="C14" s="26">
         <v>45952</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="23">
         <v>134986262</v>
       </c>
       <c r="E14" s="18">
         <v>3450110972</v>
       </c>
-      <c r="F14" s="70" t="s">
+      <c r="F14" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -3814,19 +3915,19 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="75">
+      <c r="B15" s="72">
         <v>45947</v>
       </c>
       <c r="C15" s="26">
         <v>45952</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="23">
         <v>134987136</v>
       </c>
       <c r="E15" s="18">
         <v>3450111137</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="12" t="s">
         <v>113</v>
       </c>
       <c r="G15" s="20" t="s">
@@ -3843,19 +3944,19 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="75">
+      <c r="B16" s="72">
         <v>45947</v>
       </c>
       <c r="C16" s="26">
         <v>45952</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="23">
         <v>134986230</v>
       </c>
       <c r="E16" s="18">
         <v>3450110950</v>
       </c>
-      <c r="F16" s="70" t="s">
+      <c r="F16" s="12" t="s">
         <v>115</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -3872,19 +3973,19 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="75">
+      <c r="B17" s="72">
         <v>45947</v>
       </c>
       <c r="C17" s="26">
         <v>45952</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="23">
         <v>134988232</v>
       </c>
       <c r="E17" s="18">
         <v>3450111324</v>
       </c>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="12" t="s">
         <v>117</v>
       </c>
       <c r="G17" s="20" t="s">
@@ -3901,19 +4002,19 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="75">
+      <c r="B18" s="72">
         <v>45947</v>
       </c>
       <c r="C18" s="26">
         <v>45952</v>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="23">
         <v>134988419</v>
       </c>
       <c r="E18" s="18">
         <v>3450111368</v>
       </c>
-      <c r="F18" s="70" t="s">
+      <c r="F18" s="12" t="s">
         <v>117</v>
       </c>
       <c r="G18" s="22" t="s">
@@ -3930,19 +4031,19 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="72">
         <v>45947</v>
       </c>
       <c r="C19" s="26">
         <v>45952</v>
       </c>
-      <c r="D19" s="74">
+      <c r="D19" s="23">
         <v>134993720</v>
       </c>
       <c r="E19" s="18">
         <v>3450111841</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="12" t="s">
         <v>120</v>
       </c>
       <c r="G19" s="20" t="s">
@@ -3959,19 +4060,19 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="75">
+      <c r="B20" s="72">
         <v>45947</v>
       </c>
       <c r="C20" s="26">
         <v>45952</v>
       </c>
-      <c r="D20" s="74">
+      <c r="D20" s="23">
         <v>134996719</v>
       </c>
       <c r="E20" s="18">
         <v>3450112160</v>
       </c>
-      <c r="F20" s="70" t="s">
+      <c r="F20" s="12" t="s">
         <v>122</v>
       </c>
       <c r="G20" s="20" t="s">
@@ -3994,13 +4095,13 @@
       <c r="C21" s="26">
         <v>45952</v>
       </c>
-      <c r="D21" s="74">
+      <c r="D21" s="23">
         <v>134998645</v>
       </c>
       <c r="E21" s="18">
         <v>3450112370</v>
       </c>
-      <c r="F21" s="70" t="s">
+      <c r="F21" s="12" t="s">
         <v>124</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -4023,19 +4124,19 @@
       <c r="C22" s="26">
         <v>45952</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D22" s="23">
         <v>134986172</v>
       </c>
       <c r="E22" s="18">
         <v>3450110940</v>
       </c>
-      <c r="F22" s="70" t="s">
+      <c r="F22" s="12" t="s">
         <v>126</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="76" t="s">
+      <c r="H22" s="50" t="s">
         <v>127</v>
       </c>
       <c r="I22" s="49">
@@ -4052,13 +4153,13 @@
       <c r="C23" s="26">
         <v>45952</v>
       </c>
-      <c r="D23" s="74">
+      <c r="D23" s="23">
         <v>134990611</v>
       </c>
       <c r="E23" s="18">
         <v>3450111599</v>
       </c>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="12" t="s">
         <v>128</v>
       </c>
       <c r="G23" s="20" t="s">
@@ -4081,13 +4182,13 @@
       <c r="C24" s="26">
         <v>45952</v>
       </c>
-      <c r="D24" s="74">
+      <c r="D24" s="23">
         <v>134988396</v>
       </c>
       <c r="E24" s="18">
         <v>3450111357</v>
       </c>
-      <c r="F24" s="70" t="s">
+      <c r="F24" s="12" t="s">
         <v>129</v>
       </c>
       <c r="G24" s="22" t="s">
@@ -4110,13 +4211,13 @@
       <c r="C25" s="26">
         <v>45952</v>
       </c>
-      <c r="D25" s="74">
+      <c r="D25" s="23">
         <v>135029467</v>
       </c>
       <c r="E25" s="18">
         <v>3450114580</v>
       </c>
-      <c r="F25" s="70" t="s">
+      <c r="F25" s="12" t="s">
         <v>131</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -4139,13 +4240,13 @@
       <c r="C26" s="26">
         <v>45952</v>
       </c>
-      <c r="D26" s="74">
+      <c r="D26" s="23">
         <v>134861748</v>
       </c>
       <c r="E26" s="18">
         <v>3450103118</v>
       </c>
-      <c r="F26" s="70" t="s">
+      <c r="F26" s="12" t="s">
         <v>132</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -4168,19 +4269,19 @@
       <c r="C27" s="26">
         <v>45952</v>
       </c>
-      <c r="D27" s="74">
+      <c r="D27" s="23">
         <v>134858457</v>
       </c>
       <c r="E27" s="18">
         <v>3450102744</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="12" t="s">
         <v>134</v>
       </c>
       <c r="G27" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="76" t="s">
+      <c r="H27" s="50" t="s">
         <v>135</v>
       </c>
       <c r="I27" s="49">
@@ -4197,13 +4298,13 @@
       <c r="C28" s="26">
         <v>45952</v>
       </c>
-      <c r="D28" s="74">
+      <c r="D28" s="23">
         <v>134948867</v>
       </c>
       <c r="E28" s="18">
         <v>3450107419</v>
       </c>
-      <c r="F28" s="70" t="s">
+      <c r="F28" s="12" t="s">
         <v>136</v>
       </c>
       <c r="G28" s="22" t="s">
@@ -4226,13 +4327,13 @@
       <c r="C29" s="26">
         <v>45952</v>
       </c>
-      <c r="D29" s="74">
+      <c r="D29" s="23">
         <v>135049650</v>
       </c>
       <c r="E29" s="18">
         <v>3450116428</v>
       </c>
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="12" t="s">
         <v>137</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -4255,13 +4356,13 @@
       <c r="C30" s="26">
         <v>45952</v>
       </c>
-      <c r="D30" s="74">
+      <c r="D30" s="23">
         <v>134916937</v>
       </c>
       <c r="E30" s="18">
         <v>3450106781</v>
       </c>
-      <c r="F30" s="70" t="s">
+      <c r="F30" s="12" t="s">
         <v>138</v>
       </c>
       <c r="G30" s="22" t="s">
@@ -4284,13 +4385,13 @@
       <c r="C31" s="26">
         <v>45952</v>
       </c>
-      <c r="D31" s="74">
+      <c r="D31" s="23">
         <v>134917784</v>
       </c>
       <c r="E31" s="18">
         <v>3450106870</v>
       </c>
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="12" t="s">
         <v>139</v>
       </c>
       <c r="G31" s="22" t="s">
@@ -4313,13 +4414,13 @@
       <c r="C32" s="26">
         <v>45952</v>
       </c>
-      <c r="D32" s="74">
+      <c r="D32" s="23">
         <v>134923879</v>
       </c>
       <c r="E32" s="18">
         <v>3450107177</v>
       </c>
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="12" t="s">
         <v>140</v>
       </c>
       <c r="G32" s="22" t="s">
@@ -4342,13 +4443,13 @@
       <c r="C33" s="26">
         <v>45952</v>
       </c>
-      <c r="D33" s="74">
+      <c r="D33" s="23">
         <v>134924247</v>
       </c>
       <c r="E33" s="18">
         <v>3450107232</v>
       </c>
-      <c r="F33" s="70" t="s">
+      <c r="F33" s="12" t="s">
         <v>141</v>
       </c>
       <c r="G33" s="22" t="s">
@@ -4371,13 +4472,13 @@
       <c r="C34" s="26">
         <v>45952</v>
       </c>
-      <c r="D34" s="74">
+      <c r="D34" s="23">
         <v>134928778</v>
       </c>
       <c r="E34" s="18">
         <v>3450104669</v>
       </c>
-      <c r="F34" s="70" t="s">
+      <c r="F34" s="12" t="s">
         <v>142</v>
       </c>
       <c r="G34" s="22" t="s">
@@ -4400,13 +4501,13 @@
       <c r="C35" s="26">
         <v>45952</v>
       </c>
-      <c r="D35" s="74">
+      <c r="D35" s="23">
         <v>134932121</v>
       </c>
       <c r="E35" s="18">
         <v>3450107716</v>
       </c>
-      <c r="F35" s="70" t="s">
+      <c r="F35" s="12" t="s">
         <v>143</v>
       </c>
       <c r="G35" s="22" t="s">
@@ -4429,13 +4530,13 @@
       <c r="C36" s="26">
         <v>45952</v>
       </c>
-      <c r="D36" s="74">
+      <c r="D36" s="23">
         <v>134934017</v>
       </c>
       <c r="E36" s="18">
         <v>3450107859</v>
       </c>
-      <c r="F36" s="70" t="s">
+      <c r="F36" s="12" t="s">
         <v>144</v>
       </c>
       <c r="G36" s="22" t="s">
@@ -4519,7 +4620,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4566,306 +4667,734 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D2" s="77">
+        <v>134893457</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450105087</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="49">
+        <v>45940</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C3" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D3" s="77">
+        <v>134952418</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450108761</v>
+      </c>
+      <c r="F3" s="76" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C4" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D4" s="77">
+        <v>134942055</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450108068</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45947</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D5" s="77">
+        <v>134995393</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450111984</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="49">
+        <v>45947</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D6" s="77">
+        <v>134953321</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450108805</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D7" s="77">
+        <v>135048354</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450116164</v>
+      </c>
+      <c r="F7" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="49">
+        <v>45952</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D8" s="77">
+        <v>135059123</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450117561</v>
+      </c>
+      <c r="F8" s="76" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="49">
+        <v>45952</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D9" s="77">
+        <v>134877102</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450103756</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D10" s="77">
+        <v>134877129</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450103767</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D11" s="77">
+        <v>134877739</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450103833</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="7">
+        <v>45943</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D12" s="77">
+        <v>134878367</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450103888</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="7">
+        <v>45948</v>
+      </c>
+      <c r="C13" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D13" s="77">
+        <v>134880346</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450104130</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C14" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D14" s="77">
+        <v>134890487</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450104856</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="7">
+        <v>45951</v>
+      </c>
+      <c r="C15" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D15" s="77">
+        <v>135028473</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450114437</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="78" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="49">
+        <v>45953</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="25"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C16" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D16" s="77">
+        <v>134938262</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450107936</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="25"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C17" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D17" s="77">
+        <v>134942751</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450101083</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="49">
+        <v>45937</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C18" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D18" s="77">
+        <v>134942775</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450108123</v>
+      </c>
+      <c r="F18" s="76" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D19" s="77">
+        <v>134943309</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450100995</v>
+      </c>
+      <c r="F19" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="49">
+        <v>45937</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C20" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D20" s="77">
+        <v>134943426</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450108189</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C21" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D21" s="77">
+        <v>134943641</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450108200</v>
+      </c>
+      <c r="F21" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C22" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D22" s="77">
+        <v>134948229</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450108530</v>
+      </c>
+      <c r="F22" s="76" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C23" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D23" s="77">
+        <v>134950527</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450108630</v>
+      </c>
+      <c r="F23" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C24" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D24" s="77">
+        <v>134950542</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450108640</v>
+      </c>
+      <c r="F24" s="76" t="s">
+        <v>172</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C25" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D25" s="77">
+        <v>134952625</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450108783</v>
+      </c>
+      <c r="F25" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C26" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D26" s="77">
+        <v>134953465</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450108816</v>
+      </c>
+      <c r="F26" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="49">
+        <v>45945</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
     </row>
@@ -5089,77 +5618,17 @@
       <c r="G49" s="6"/>
       <c r="H49" s="9"/>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A26" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7117,60 +7586,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="0b21122b788e66690c7828fa6fbd4a35">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8036ee6e27b0b3bdae29363f3ddd68e9" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7219,12 +7636,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -7233,12 +7650,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -7321,7 +7738,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7340,7 +7757,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7373,7 +7790,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7456,8 +7873,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7546,7 +7963,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -7596,18 +8013,70 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96D15F45-B9F7-4EA9-9771-940F36B11EA0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6A422DA-5A64-429E-A048-04B376314D8C}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 20.10.2025 a 26.10.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC4D956E-1B0A-4881-ABE3-1B71E206A5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C704822-48B0-498E-9E96-C2735FC0A08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="225">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -592,12 +592,175 @@
   <si>
     <t xml:space="preserve">43 468 393 ALESSANDRO MIRANDA COIMBRA ME     </t>
   </si>
+  <si>
+    <t>EDMILO MIRANDA BARBOSA CPF- 03102584136</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t>22/10/2025</t>
+  </si>
+  <si>
+    <t>FABIO DE MEDEIROS OLIVEIRA CPF-98100823472</t>
+  </si>
+  <si>
+    <t>NUP 23/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO APARECIDO LEME                       </t>
+  </si>
+  <si>
+    <t>19/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEANE ROCHA BANDEIRA                         </t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA DA COSTA MENDES ANTUNES               </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 23/10/2025</t>
+  </si>
+  <si>
+    <t>23/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGE DA SILVA MARQUES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIVANEIDE JERONIMO BEZERRA DA SILVA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 031 429 ALYSON RODRIGO FERREIRA ME        </t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria prévia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE FRANCA LOPES DOS SANTOS            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORRACHARIA DO VANDO LTDA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO CHIPOLLINO AQUINES                     </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURO INDUSTRIA COMERCIO E SERVICOS LTDA EPP  </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não h
+á possibilidade efetuar a transferência de bônus para a empresa EU
+RO INDUSTRIA COMERCIO E SERVICOS LTDA,pois o(a) senhor(a) LOHRANE
+PATRICIA FERREIRA BRITO, não consta no quadro de sócios da empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO LINDENBERG RODRIGUES DOS SANTOS      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO DE SANTANA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSSANA MONTEIRO DA COSTA SEIXAS             </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t>INDUSTRIA E COMERCIO DE CONFECCOES ARAUJO CHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCIDES PAES DO PRADO JUNIOR                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO MOREIRA DOS SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARCIO JHONATAN DA SILVA MORAES              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELLA BABY CONFECCOES LTDA ME                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRLANDIA DA SILVA GALVAO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO BANDEIRA DE SOUZA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALQUIRIA FERREIRA DE SOUSA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLEISON RAMOS DE CARVALHO                    </t>
+  </si>
+  <si>
+    <t>Aceitação condicionada à confirmação de bônus na CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDIVAN FRANCA DO NASCIMENTO                </t>
+  </si>
+  <si>
+    <t>NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO. FOTO INCORRETA: Frente e lateral do pass, Frente e lateral do mot, Traseira e lateral do mot, Traseira e lateral do pass, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAYLLA DE SOUSA MENDES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F DA SILVA LEANDRO ME                        </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do pass, Frente e lateral do mot, Traseira e lateral do mot, Traseira e lateral do pasS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAQUELINE FAVARO FERREIRA                    </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELENIR CUCHI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILSON RIBEIRO DUARTE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ DONIZETI CARNEIRO                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise: Cópia da apólice congênere c
+om vigência de 2025 a 2026; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO CARLOS OLIVEIRA PIRES                </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:Cópia da apólice congênere c
+om vigência de 2025 a 2026. Endosso de cancelamento emitido</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,11 +786,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -661,7 +819,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -867,12 +1025,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -950,34 +1119,12 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1061,17 +1208,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1456,7 +1641,7 @@
       <c r="D2" s="23">
         <v>134920718</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="35">
         <v>3450107023</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -1465,10 +1650,10 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="49">
+      <c r="I2" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1485,7 +1670,7 @@
       <c r="D3" s="23">
         <v>134926193</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="36">
         <v>3450107364</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1494,10 +1679,10 @@
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="49">
+      <c r="I3" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1514,7 +1699,7 @@
       <c r="D4" s="23">
         <v>134927129</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="36">
         <v>3450107397</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1523,39 +1708,39 @@
       <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="49">
+      <c r="I4" s="39">
         <v>45944</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="63" customFormat="1">
-      <c r="A5" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="55">
+    <row r="5" spans="1:9" s="53" customFormat="1">
+      <c r="A5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="45">
         <v>45944</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="46">
         <v>45950</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="47">
         <v>134924632</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="48">
         <v>3450107287</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="60" t="s">
+      <c r="G5" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="52">
         <v>45944</v>
       </c>
     </row>
@@ -1572,7 +1757,7 @@
       <c r="D6" s="23">
         <v>134943152</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="36">
         <v>3450101006</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1581,10 +1766,10 @@
       <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="39">
         <v>45937</v>
       </c>
     </row>
@@ -1601,7 +1786,7 @@
       <c r="D7" s="23">
         <v>134946354</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="36">
         <v>3450108431</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1610,10 +1795,10 @@
       <c r="G7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -1630,7 +1815,7 @@
       <c r="D8" s="23">
         <v>134948123</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="36">
         <v>3450108519</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1639,10 +1824,10 @@
       <c r="G8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -1659,7 +1844,7 @@
       <c r="D9" s="23">
         <v>134946767</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="36">
         <v>3450108453</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1668,10 +1853,10 @@
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -1688,7 +1873,7 @@
       <c r="D10" s="23">
         <v>134954190</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="36">
         <v>3450108904</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1697,10 +1882,10 @@
       <c r="G10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -1717,7 +1902,7 @@
       <c r="D11" s="23">
         <v>134948164</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="36">
         <v>3450108520</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1726,10 +1911,10 @@
       <c r="G11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -1746,7 +1931,7 @@
       <c r="D12" s="23">
         <v>134899850</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="36">
         <v>3450105307</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1755,10 +1940,10 @@
       <c r="G12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -1775,7 +1960,7 @@
       <c r="D13" s="23">
         <v>134980185</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="36">
         <v>3450110510</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1784,10 +1969,10 @@
       <c r="G13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -1804,7 +1989,7 @@
       <c r="D14" s="23">
         <v>134926575</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="36">
         <v>3450107386</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1813,10 +1998,10 @@
       <c r="G14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1833,7 +2018,7 @@
       <c r="D15" s="23">
         <v>134912411</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="36">
         <v>3450106517</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1842,10 +2027,10 @@
       <c r="G15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -1862,7 +2047,7 @@
       <c r="D16" s="23">
         <v>134933365</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="36">
         <v>3450107793</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1871,10 +2056,10 @@
       <c r="G16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1891,7 +2076,7 @@
       <c r="D17" s="23">
         <v>134923813</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="36">
         <v>3450107166</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1900,10 +2085,10 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1920,7 +2105,7 @@
       <c r="D18" s="23">
         <v>134873058</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="36">
         <v>3450100324</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1929,10 +2114,10 @@
       <c r="G18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="H18" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="39">
         <v>45936</v>
       </c>
     </row>
@@ -1949,7 +2134,7 @@
       <c r="D19" s="23">
         <v>134934767</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="36">
         <v>3450107870</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1958,10 +2143,10 @@
       <c r="G19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -1969,8 +2154,8 @@
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="47"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="37"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="9"/>
@@ -1982,7 +2167,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="23"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="48"/>
+      <c r="F21" s="38"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
       <c r="I21" s="25"/>
@@ -2443,7 +2628,7 @@
         <v>26</v>
       </c>
       <c r="H2" s="12"/>
-      <c r="I2" s="49"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -2468,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="I3" s="49"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2493,7 +2678,7 @@
         <v>26</v>
       </c>
       <c r="H4" s="13"/>
-      <c r="I4" s="49"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -2505,10 +2690,10 @@
       <c r="C5" s="26">
         <v>45951</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="55">
         <v>3450101985</v>
       </c>
       <c r="F5" s="29" t="s">
@@ -2518,7 +2703,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="13"/>
-      <c r="I5" s="49"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -2545,7 +2730,7 @@
       <c r="H6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -2574,7 +2759,7 @@
       <c r="H7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2603,7 +2788,7 @@
       <c r="H8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2632,7 +2817,7 @@
       <c r="H9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2661,7 +2846,7 @@
       <c r="H10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2690,7 +2875,7 @@
       <c r="H11" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="39">
         <v>45950</v>
       </c>
     </row>
@@ -2719,7 +2904,7 @@
       <c r="H12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="39">
         <v>45946</v>
       </c>
     </row>
@@ -2748,7 +2933,7 @@
       <c r="H13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2777,7 +2962,7 @@
       <c r="H14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="39">
         <v>45950</v>
       </c>
     </row>
@@ -2806,7 +2991,7 @@
       <c r="H15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -2835,7 +3020,7 @@
       <c r="H16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -2864,7 +3049,7 @@
       <c r="H17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="39">
         <v>45950</v>
       </c>
     </row>
@@ -2893,7 +3078,7 @@
       <c r="H18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -2922,7 +3107,7 @@
       <c r="H19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="39">
         <v>45950</v>
       </c>
     </row>
@@ -2951,7 +3136,7 @@
       <c r="H20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -2980,7 +3165,7 @@
       <c r="H21" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="39">
         <v>45946</v>
       </c>
     </row>
@@ -3009,7 +3194,7 @@
       <c r="H22" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="49">
+      <c r="I22" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -3038,7 +3223,7 @@
       <c r="H23" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="49">
+      <c r="I23" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -3067,7 +3252,7 @@
       <c r="H24" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="39">
         <v>45951</v>
       </c>
     </row>
@@ -3096,7 +3281,7 @@
       <c r="H25" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="49">
+      <c r="I25" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -3122,10 +3307,10 @@
       <c r="G26" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="67" t="s">
+      <c r="H26" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="49">
+      <c r="I26" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -3154,7 +3339,7 @@
       <c r="H27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I27" s="49">
+      <c r="I27" s="39">
         <v>45938</v>
       </c>
     </row>
@@ -3183,7 +3368,7 @@
       <c r="H28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -3191,9 +3376,9 @@
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="26"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="31"/>
       <c r="G29" s="20"/>
       <c r="H29" s="15"/>
       <c r="I29" s="25"/>
@@ -3559,19 +3744,19 @@
       <c r="D2" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="58">
         <v>3450112590</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="63" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="49"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -3586,19 +3771,19 @@
       <c r="D3" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="59">
         <v>3450112666</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="63" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="I3" s="49"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3613,19 +3798,19 @@
       <c r="D4" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="59">
         <v>3450112193</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="63" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="49"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3640,19 +3825,19 @@
       <c r="D5" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="59">
         <v>3450111533</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="63" t="s">
         <v>94</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="49"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3667,52 +3852,52 @@
       <c r="D6" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="59">
         <v>3450114162</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="63" t="s">
         <v>96</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="49"/>
+      <c r="I6" s="39"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="62">
         <v>45936</v>
       </c>
       <c r="C7" s="26">
         <v>45952</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="59">
         <v>3450100160</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="64" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="49"/>
+      <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="62">
         <v>45938</v>
       </c>
       <c r="C8" s="26">
@@ -3721,19 +3906,19 @@
       <c r="D8" s="23">
         <v>134849892</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="60">
         <v>3450102436</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="65" t="s">
         <v>101</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -3741,7 +3926,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="62">
         <v>45944</v>
       </c>
       <c r="C9" s="26">
@@ -3759,10 +3944,10 @@
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="39">
         <v>45951</v>
       </c>
     </row>
@@ -3770,7 +3955,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="62">
         <v>45943</v>
       </c>
       <c r="C10" s="26">
@@ -3788,10 +3973,10 @@
       <c r="G10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -3799,7 +3984,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="72">
+      <c r="B11" s="62">
         <v>45940</v>
       </c>
       <c r="C11" s="26">
@@ -3817,10 +4002,10 @@
       <c r="G11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -3828,7 +4013,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="62">
         <v>45946</v>
       </c>
       <c r="C12" s="26">
@@ -3846,10 +4031,10 @@
       <c r="G12" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="39">
         <v>45946</v>
       </c>
     </row>
@@ -3857,7 +4042,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="62">
         <v>45946</v>
       </c>
       <c r="C13" s="26">
@@ -3875,10 +4060,10 @@
       <c r="G13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="39">
         <v>45946</v>
       </c>
     </row>
@@ -3886,7 +4071,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="62">
         <v>45947</v>
       </c>
       <c r="C14" s="26">
@@ -3904,10 +4089,10 @@
       <c r="G14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -3915,7 +4100,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="62">
         <v>45947</v>
       </c>
       <c r="C15" s="26">
@@ -3933,10 +4118,10 @@
       <c r="G15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -3944,7 +4129,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="62">
         <v>45947</v>
       </c>
       <c r="C16" s="26">
@@ -3962,10 +4147,10 @@
       <c r="G16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -3973,7 +4158,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="72">
+      <c r="B17" s="62">
         <v>45947</v>
       </c>
       <c r="C17" s="26">
@@ -3991,10 +4176,10 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4002,7 +4187,7 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="62">
         <v>45947</v>
       </c>
       <c r="C18" s="26">
@@ -4020,10 +4205,10 @@
       <c r="G18" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="H18" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4031,7 +4216,7 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="62">
         <v>45947</v>
       </c>
       <c r="C19" s="26">
@@ -4049,10 +4234,10 @@
       <c r="G19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4060,7 +4245,7 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="72">
+      <c r="B20" s="62">
         <v>45947</v>
       </c>
       <c r="C20" s="26">
@@ -4078,10 +4263,10 @@
       <c r="G20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4107,10 +4292,10 @@
       <c r="G21" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4136,10 +4321,10 @@
       <c r="G22" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="49">
+      <c r="I22" s="39">
         <v>45952</v>
       </c>
     </row>
@@ -4165,10 +4350,10 @@
       <c r="G23" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="H23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="49">
+      <c r="I23" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4194,10 +4379,10 @@
       <c r="G24" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="50" t="s">
+      <c r="H24" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4223,10 +4408,10 @@
       <c r="G25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="49">
+      <c r="I25" s="39">
         <v>45951</v>
       </c>
     </row>
@@ -4252,10 +4437,10 @@
       <c r="G26" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="H26" s="50" t="s">
+      <c r="H26" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="I26" s="49">
+      <c r="I26" s="39">
         <v>45943</v>
       </c>
     </row>
@@ -4281,10 +4466,10 @@
       <c r="G27" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="50" t="s">
+      <c r="H27" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="49">
+      <c r="I27" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4310,10 +4495,10 @@
       <c r="G28" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="50" t="s">
+      <c r="H28" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4339,10 +4524,10 @@
       <c r="G29" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="50" t="s">
+      <c r="H29" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="49">
+      <c r="I29" s="39">
         <v>45952</v>
       </c>
     </row>
@@ -4368,10 +4553,10 @@
       <c r="G30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="50" t="s">
+      <c r="H30" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I30" s="49">
+      <c r="I30" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4397,10 +4582,10 @@
       <c r="G31" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="50" t="s">
+      <c r="H31" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I31" s="49">
+      <c r="I31" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4426,10 +4611,10 @@
       <c r="G32" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="50" t="s">
+      <c r="H32" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I32" s="49">
+      <c r="I32" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4455,10 +4640,10 @@
       <c r="G33" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="50" t="s">
+      <c r="H33" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I33" s="49">
+      <c r="I33" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4484,10 +4669,10 @@
       <c r="G34" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="50" t="s">
+      <c r="H34" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I34" s="49">
+      <c r="I34" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -4513,10 +4698,10 @@
       <c r="G35" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="50" t="s">
+      <c r="H35" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I35" s="49">
+      <c r="I35" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4542,10 +4727,10 @@
       <c r="G36" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="50" t="s">
+      <c r="H36" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I36" s="49">
+      <c r="I36" s="39">
         <v>45944</v>
       </c>
     </row>
@@ -4673,22 +4858,22 @@
       <c r="C2" s="26">
         <v>45953</v>
       </c>
-      <c r="D2" s="77">
+      <c r="D2" s="23">
         <v>134893457</v>
       </c>
       <c r="E2" s="18">
         <v>3450105087</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="12" t="s">
         <v>145</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="49">
+      <c r="I2" s="39">
         <v>45940</v>
       </c>
     </row>
@@ -4702,22 +4887,22 @@
       <c r="C3" s="26">
         <v>45953</v>
       </c>
-      <c r="D3" s="77">
+      <c r="D3" s="23">
         <v>134952418</v>
       </c>
       <c r="E3" s="18">
         <v>3450108761</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="12" t="s">
         <v>146</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="49">
+      <c r="I3" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -4731,22 +4916,22 @@
       <c r="C4" s="26">
         <v>45953</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="23">
         <v>134942055</v>
       </c>
       <c r="E4" s="18">
         <v>3450108068</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="12" t="s">
         <v>147</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="49">
+      <c r="I4" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -4760,22 +4945,22 @@
       <c r="C5" s="26">
         <v>45953</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="23">
         <v>134995393</v>
       </c>
       <c r="E5" s="18">
         <v>3450111984</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="12" t="s">
         <v>148</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="39">
         <v>45947</v>
       </c>
     </row>
@@ -4789,22 +4974,22 @@
       <c r="C6" s="26">
         <v>45953</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="23">
         <v>134953321</v>
       </c>
       <c r="E6" s="18">
         <v>3450108805</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="12" t="s">
         <v>149</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -4818,22 +5003,22 @@
       <c r="C7" s="26">
         <v>45953</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="23">
         <v>135048354</v>
       </c>
       <c r="E7" s="18">
         <v>3450116164</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="39">
         <v>45952</v>
       </c>
     </row>
@@ -4847,22 +5032,22 @@
       <c r="C8" s="26">
         <v>45953</v>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="23">
         <v>135059123</v>
       </c>
       <c r="E8" s="18">
         <v>3450117561</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="12" t="s">
         <v>150</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="39">
         <v>45952</v>
       </c>
     </row>
@@ -4876,22 +5061,22 @@
       <c r="C9" s="26">
         <v>45953</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="23">
         <v>134877102</v>
       </c>
       <c r="E9" s="18">
         <v>3450103756</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="12" t="s">
         <v>151</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -4905,22 +5090,22 @@
       <c r="C10" s="26">
         <v>45953</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="23">
         <v>134877129</v>
       </c>
       <c r="E10" s="18">
         <v>3450103767</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="12" t="s">
         <v>153</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -4934,22 +5119,22 @@
       <c r="C11" s="26">
         <v>45953</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="23">
         <v>134877739</v>
       </c>
       <c r="E11" s="18">
         <v>3450103833</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="12" t="s">
         <v>155</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -4963,22 +5148,22 @@
       <c r="C12" s="26">
         <v>45953</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="23">
         <v>134878367</v>
       </c>
       <c r="E12" s="18">
         <v>3450103888</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="12" t="s">
         <v>157</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -4992,22 +5177,22 @@
       <c r="C13" s="26">
         <v>45953</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="23">
         <v>134880346</v>
       </c>
       <c r="E13" s="18">
         <v>3450104130</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="12" t="s">
         <v>158</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -5021,22 +5206,22 @@
       <c r="C14" s="26">
         <v>45953</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="23">
         <v>134890487</v>
       </c>
       <c r="E14" s="18">
         <v>3450104856</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="12" t="s">
         <v>160</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -5050,22 +5235,22 @@
       <c r="C15" s="26">
         <v>45953</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="23">
         <v>135028473</v>
       </c>
       <c r="E15" s="18">
         <v>3450114437</v>
       </c>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="12" t="s">
         <v>162</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="78" t="s">
+      <c r="H15" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -5079,22 +5264,22 @@
       <c r="C16" s="26">
         <v>45953</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="23">
         <v>134938262</v>
       </c>
       <c r="E16" s="18">
         <v>3450107936</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="12" t="s">
         <v>164</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5108,22 +5293,22 @@
       <c r="C17" s="26">
         <v>45953</v>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="23">
         <v>134942751</v>
       </c>
       <c r="E17" s="18">
         <v>3450101083</v>
       </c>
-      <c r="F17" s="76" t="s">
+      <c r="F17" s="12" t="s">
         <v>165</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="39">
         <v>45937</v>
       </c>
     </row>
@@ -5137,22 +5322,22 @@
       <c r="C18" s="26">
         <v>45953</v>
       </c>
-      <c r="D18" s="77">
+      <c r="D18" s="23">
         <v>134942775</v>
       </c>
       <c r="E18" s="18">
         <v>3450108123</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="12" t="s">
         <v>166</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="H18" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5166,22 +5351,22 @@
       <c r="C19" s="26">
         <v>45953</v>
       </c>
-      <c r="D19" s="77">
+      <c r="D19" s="23">
         <v>134943309</v>
       </c>
       <c r="E19" s="18">
         <v>3450100995</v>
       </c>
-      <c r="F19" s="76" t="s">
+      <c r="F19" s="12" t="s">
         <v>167</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="39">
         <v>45937</v>
       </c>
     </row>
@@ -5195,22 +5380,22 @@
       <c r="C20" s="26">
         <v>45953</v>
       </c>
-      <c r="D20" s="77">
+      <c r="D20" s="23">
         <v>134943426</v>
       </c>
       <c r="E20" s="18">
         <v>3450108189</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="12" t="s">
         <v>168</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5224,22 +5409,22 @@
       <c r="C21" s="26">
         <v>45953</v>
       </c>
-      <c r="D21" s="77">
+      <c r="D21" s="23">
         <v>134943641</v>
       </c>
       <c r="E21" s="18">
         <v>3450108200</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="12" t="s">
         <v>169</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5253,22 +5438,22 @@
       <c r="C22" s="26">
         <v>45953</v>
       </c>
-      <c r="D22" s="77">
+      <c r="D22" s="23">
         <v>134948229</v>
       </c>
       <c r="E22" s="18">
         <v>3450108530</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="12" t="s">
         <v>170</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="49">
+      <c r="I22" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5282,22 +5467,22 @@
       <c r="C23" s="26">
         <v>45953</v>
       </c>
-      <c r="D23" s="77">
+      <c r="D23" s="23">
         <v>134950527</v>
       </c>
       <c r="E23" s="18">
         <v>3450108630</v>
       </c>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="12" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="H23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="49">
+      <c r="I23" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5311,22 +5496,22 @@
       <c r="C24" s="26">
         <v>45953</v>
       </c>
-      <c r="D24" s="77">
+      <c r="D24" s="23">
         <v>134950542</v>
       </c>
       <c r="E24" s="18">
         <v>3450108640</v>
       </c>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="12" t="s">
         <v>172</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="50" t="s">
+      <c r="H24" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5340,22 +5525,22 @@
       <c r="C25" s="26">
         <v>45953</v>
       </c>
-      <c r="D25" s="77">
+      <c r="D25" s="23">
         <v>134952625</v>
       </c>
       <c r="E25" s="18">
         <v>3450108783</v>
       </c>
-      <c r="F25" s="76" t="s">
+      <c r="F25" s="12" t="s">
         <v>173</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="49">
+      <c r="I25" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5369,22 +5554,22 @@
       <c r="C26" s="26">
         <v>45953</v>
       </c>
-      <c r="D26" s="77">
+      <c r="D26" s="23">
         <v>134953465</v>
       </c>
       <c r="E26" s="18">
         <v>3450108816</v>
       </c>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="12" t="s">
         <v>174</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="50" t="s">
+      <c r="H26" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="49">
+      <c r="I26" s="39">
         <v>45945</v>
       </c>
     </row>
@@ -5638,7 +5823,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -5674,7 +5859,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5685,287 +5870,645 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450119068</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="55">
+        <v>3450117100</v>
+      </c>
+      <c r="F3" s="73" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D4" s="23">
+        <v>134972460</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450110114</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="39">
+        <v>45946</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D5" s="23">
+        <v>135004830</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450112710</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="39">
+        <v>45949</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D6" s="23">
+        <v>135038927</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450115548</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>185</v>
+      </c>
+      <c r="I6" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D7" s="23">
+        <v>135049107</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450116340</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D8" s="23">
+        <v>135049760</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450116440</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="39">
+        <v>45952</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D9" s="23">
+        <v>135061542</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450117760</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="I9" s="39">
+        <v>45952</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D10" s="23">
+        <v>135044623</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450115845</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="39">
+        <v>45952</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D11" s="23">
+        <v>135077889</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450119002</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D12" s="23">
+        <v>135068531</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450118133</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C13" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D13" s="23">
+        <v>134887384</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450104647</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13" s="39">
+        <v>45940</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C14" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D14" s="23">
+        <v>134943834</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450100930</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="39">
+        <v>45944</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="25"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="25"/>
+      <c r="B15" s="7">
+        <v>45975</v>
+      </c>
+      <c r="C15" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D15" s="23">
+        <v>135017663</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450113690</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="39">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1">
+      <c r="A16" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45941</v>
+      </c>
+      <c r="C16" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D16" s="23">
+        <v>134892653</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450105000</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="70" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="39">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C17" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D17" s="23">
+        <v>134921005</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450107045</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="39">
+        <v>45954</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="25"/>
+      <c r="B18" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C18" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D18" s="23">
+        <v>135093130</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450120168</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="39">
+        <v>45954</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D19" s="23">
+        <v>134960181</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450108475</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="39">
+        <v>45945</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C20" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D20" s="23">
+        <v>134962517</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450109234</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="39">
+        <v>45946</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C21" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D21" s="23">
+        <v>134963068</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450109322</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="39">
+        <v>45946</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="25"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C22" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D22" s="23">
+        <v>134964653</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450109443</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="39">
+        <v>45954</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="25"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C23" s="26">
+        <v>45954</v>
+      </c>
+      <c r="D23" s="23">
+        <v>134972256</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450110070</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="39">
+        <v>45946</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="9"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
@@ -6087,7 +6630,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="25"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6298,28 +6841,17 @@
       <c r="H54" s="9"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6329,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -6375,171 +6907,358 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45941</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D2" s="23">
+        <v>134923009</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450105043</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="39">
+        <v>45941</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="35"/>
+      <c r="B3" s="7">
+        <v>45950</v>
+      </c>
+      <c r="C3" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D3" s="23">
+        <v>135019481</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450113865</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="77">
+        <v>45955</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C4" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D4" s="23">
+        <v>134923904</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450107200</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" s="39">
+        <v>45955</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D5" s="23">
+        <v>135055061</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450117033</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="I5" s="39">
+        <v>45952</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D6" s="23">
+        <v>134885465</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450104450</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="39">
+        <v>45954</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D7" s="23">
+        <v>135045948</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450115944</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="39">
+        <v>45952</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D8" s="23">
+        <v>134876730</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450103734</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D9" s="23">
+        <v>135085387</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450119222</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D10" s="23">
+        <v>134879652</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450104020</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D11" s="23">
+        <v>134880056</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450104097</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="39">
+        <v>45955</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45955</v>
+      </c>
+      <c r="D12" s="23">
+        <v>134887332</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450104614</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" s="39">
+        <v>45953</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
     </row>
@@ -6549,7 +7268,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
     </row>
@@ -6823,98 +7542,21 @@
       <c r="G44" s="6"/>
       <c r="H44" s="9"/>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A12" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+      <formula1>$J$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
-      <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7586,8 +8228,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="da42b8270fd9829a6a8b9b6d410a91d7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="934d0cac02f3d216c96e26d9eebd9738" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7964,6 +8606,58 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -8013,64 +8707,12 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496598</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496598</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496598</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96D15F45-B9F7-4EA9-9771-940F36B11EA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F1C859E-1F49-4824-B27F-2A6CAA9B5017}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8078,5 +8720,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>